--- a/assets/docs/lop2/Am nhac - Lop 2.xlsx
+++ b/assets/docs/lop2/Am nhac - Lop 2.xlsx
@@ -644,7 +644,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 1: Sắc màu âm thanh — Ôn tập: Hát và Đọc nhạc; Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -915,7 +915,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 3: Mái trường thân yêu — Ôn tập: Hát và Đọc nhạc; Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối học kì I</t>
+          <t>Ôn tập cuối học kì I (tiết 1)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối học kì I</t>
+          <t>Ôn tập cuối học kì I (tiết 2)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 5: Mùa xuân — Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1515,7 +1515,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 7: Những con vật quanh em — Ôn tập: Hát và đọc nhạc; Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
